--- a/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SÚPER AGROPAL PALENCIA.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SÚPER AGROPAL PALENCIA.xlsx
@@ -565,13 +565,13 @@
         <v>32</v>
       </c>
       <c r="D2" t="n">
-        <v>80.8682</v>
+        <v>78.4208</v>
       </c>
       <c r="E2" t="n">
-        <v>57.7138</v>
+        <v>56.0524</v>
       </c>
       <c r="F2" t="n">
-        <v>23.1544</v>
+        <v>22.3689</v>
       </c>
       <c r="G2" t="n">
         <v>26.7454</v>
@@ -610,13 +610,13 @@
         <v>55.2468</v>
       </c>
       <c r="S2" t="n">
-        <v>11.3776</v>
+        <v>8.930400000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>4.562</v>
+        <v>2.8999</v>
       </c>
       <c r="U2" t="n">
-        <v>6.816000000000001</v>
+        <v>6.0303</v>
       </c>
       <c r="V2" t="n">
         <v>14.034</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>I. JAKOVICS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>32</v>
       </c>
       <c r="D3" t="n">
-        <v>66.2043</v>
+        <v>71.03100000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>34.3064</v>
+        <v>49.8348</v>
       </c>
       <c r="F3" t="n">
-        <v>31.8981</v>
+        <v>21.1961</v>
       </c>
       <c r="G3" t="n">
-        <v>31.6638</v>
+        <v>41.8846</v>
       </c>
       <c r="H3" t="n">
-        <v>15.1926</v>
+        <v>8.073599999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>16.4707</v>
+        <v>33.81140000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>50.4009</v>
+        <v>59.5243</v>
       </c>
       <c r="K3" t="n">
-        <v>26.4597</v>
+        <v>20.5173</v>
       </c>
       <c r="L3" t="n">
-        <v>23.9414</v>
+        <v>39.0067</v>
       </c>
       <c r="M3" t="n">
-        <v>-18.7373</v>
+        <v>-17.6394</v>
       </c>
       <c r="N3" t="n">
-        <v>-11.2673</v>
+        <v>-12.4444</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.470400000000001</v>
+        <v>-5.1953</v>
       </c>
       <c r="P3" t="n">
-        <v>21.533</v>
+        <v>3.2623</v>
       </c>
       <c r="Q3" t="n">
-        <v>-33.4958</v>
+        <v>-50.6789</v>
       </c>
       <c r="R3" t="n">
-        <v>55.0293</v>
+        <v>53.9415</v>
       </c>
       <c r="S3" t="n">
-        <v>12.4791</v>
+        <v>-0.2235999999999998</v>
       </c>
       <c r="T3" t="n">
-        <v>4.477899999999999</v>
+        <v>-1.1594</v>
       </c>
       <c r="U3" t="n">
-        <v>8.001300000000001</v>
+        <v>0.9357000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5282000000000003</v>
+        <v>26.107</v>
       </c>
       <c r="W3" t="n">
-        <v>12.9236</v>
+        <v>42.1492</v>
       </c>
       <c r="X3" t="n">
-        <v>-12.3953</v>
+        <v>-16.042</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. JAKOVICS</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>32</v>
       </c>
       <c r="D4" t="n">
-        <v>52.9094</v>
+        <v>64.2762</v>
       </c>
       <c r="E4" t="n">
-        <v>35.9875</v>
+        <v>33.7548</v>
       </c>
       <c r="F4" t="n">
-        <v>16.9216</v>
+        <v>30.5212</v>
       </c>
       <c r="G4" t="n">
-        <v>41.8846</v>
+        <v>31.6638</v>
       </c>
       <c r="H4" t="n">
-        <v>8.073599999999999</v>
+        <v>15.1926</v>
       </c>
       <c r="I4" t="n">
-        <v>33.81140000000001</v>
+        <v>16.4707</v>
       </c>
       <c r="J4" t="n">
-        <v>59.5243</v>
+        <v>50.4009</v>
       </c>
       <c r="K4" t="n">
-        <v>20.5173</v>
+        <v>26.4597</v>
       </c>
       <c r="L4" t="n">
-        <v>39.0067</v>
+        <v>23.9414</v>
       </c>
       <c r="M4" t="n">
-        <v>-17.6394</v>
+        <v>-18.7373</v>
       </c>
       <c r="N4" t="n">
-        <v>-12.4444</v>
+        <v>-11.2673</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.1953</v>
+        <v>-7.470400000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>3.2623</v>
+        <v>21.533</v>
       </c>
       <c r="Q4" t="n">
-        <v>-50.6789</v>
+        <v>-33.4958</v>
       </c>
       <c r="R4" t="n">
-        <v>53.9415</v>
+        <v>55.0293</v>
       </c>
       <c r="S4" t="n">
-        <v>-18.3451</v>
+        <v>10.5511</v>
       </c>
       <c r="T4" t="n">
-        <v>-15.0063</v>
+        <v>3.9263</v>
       </c>
       <c r="U4" t="n">
-        <v>-3.3385</v>
+        <v>6.6248</v>
       </c>
       <c r="V4" t="n">
-        <v>26.107</v>
+        <v>0.5282000000000003</v>
       </c>
       <c r="W4" t="n">
-        <v>42.1492</v>
+        <v>12.9236</v>
       </c>
       <c r="X4" t="n">
-        <v>-16.042</v>
+        <v>-12.3953</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. WINTERING</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="n">
-        <v>49.5467</v>
+        <v>54.0519</v>
       </c>
       <c r="E5" t="n">
-        <v>30.9398</v>
+        <v>21.7583</v>
       </c>
       <c r="F5" t="n">
-        <v>18.6065</v>
+        <v>32.2933</v>
       </c>
       <c r="G5" t="n">
-        <v>38.1036</v>
+        <v>39.9329</v>
       </c>
       <c r="H5" t="n">
-        <v>16.6715</v>
+        <v>2.8118</v>
       </c>
       <c r="I5" t="n">
-        <v>21.4324</v>
+        <v>37.1209</v>
       </c>
       <c r="J5" t="n">
-        <v>52.0741</v>
+        <v>54.7275</v>
       </c>
       <c r="K5" t="n">
-        <v>23.922</v>
+        <v>13.3003</v>
       </c>
       <c r="L5" t="n">
-        <v>28.152</v>
+        <v>41.4271</v>
       </c>
       <c r="M5" t="n">
-        <v>-13.9706</v>
+        <v>-14.7947</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.2507</v>
+        <v>-10.4879</v>
       </c>
       <c r="O5" t="n">
-        <v>-6.7197</v>
+        <v>-4.3063</v>
       </c>
       <c r="P5" t="n">
-        <v>5.6552</v>
+        <v>3.9147</v>
       </c>
       <c r="Q5" t="n">
-        <v>-41.7612</v>
+        <v>-53.0716</v>
       </c>
       <c r="R5" t="n">
-        <v>47.4166</v>
+        <v>56.9869</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8512</v>
+        <v>3.8739</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9453000000000005</v>
+        <v>0.3990999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>2.796600000000001</v>
+        <v>3.4746</v>
       </c>
       <c r="V5" t="n">
-        <v>3.9367</v>
+        <v>6.3304</v>
       </c>
       <c r="W5" t="n">
-        <v>21.5728</v>
+        <v>19.7034</v>
       </c>
       <c r="X5" t="n">
-        <v>-17.6365</v>
+        <v>-13.3733</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>A. WINTERING</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" t="n">
-        <v>33.5978</v>
+        <v>53.9302</v>
       </c>
       <c r="E6" t="n">
-        <v>8.805199999999999</v>
+        <v>33.4994</v>
       </c>
       <c r="F6" t="n">
-        <v>24.7925</v>
+        <v>20.4305</v>
       </c>
       <c r="G6" t="n">
-        <v>39.9329</v>
+        <v>38.1036</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8118</v>
+        <v>16.6715</v>
       </c>
       <c r="I6" t="n">
-        <v>37.1209</v>
+        <v>21.4324</v>
       </c>
       <c r="J6" t="n">
-        <v>54.7275</v>
+        <v>52.0741</v>
       </c>
       <c r="K6" t="n">
-        <v>13.3003</v>
+        <v>23.922</v>
       </c>
       <c r="L6" t="n">
-        <v>41.4271</v>
+        <v>28.152</v>
       </c>
       <c r="M6" t="n">
-        <v>-14.7947</v>
+        <v>-13.9706</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.4879</v>
+        <v>-7.2507</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.3063</v>
+        <v>-6.7197</v>
       </c>
       <c r="P6" t="n">
-        <v>3.9147</v>
+        <v>5.6552</v>
       </c>
       <c r="Q6" t="n">
-        <v>-53.0716</v>
+        <v>-41.7612</v>
       </c>
       <c r="R6" t="n">
-        <v>56.9869</v>
+        <v>47.4166</v>
       </c>
       <c r="S6" t="n">
-        <v>-16.5799</v>
+        <v>6.2351</v>
       </c>
       <c r="T6" t="n">
-        <v>-12.5536</v>
+        <v>1.6145</v>
       </c>
       <c r="U6" t="n">
-        <v>-4.0264</v>
+        <v>4.6206</v>
       </c>
       <c r="V6" t="n">
-        <v>6.3304</v>
+        <v>3.9367</v>
       </c>
       <c r="W6" t="n">
-        <v>19.7034</v>
+        <v>21.5728</v>
       </c>
       <c r="X6" t="n">
-        <v>-13.3733</v>
+        <v>-17.6365</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>V. VUCETIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D7" t="n">
-        <v>27.1067</v>
+        <v>21.0943</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.308899999999999</v>
+        <v>13.6243</v>
       </c>
       <c r="F7" t="n">
-        <v>28.4155</v>
+        <v>7.4697</v>
       </c>
       <c r="G7" t="n">
-        <v>3.133900000000001</v>
+        <v>2.2043</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.1168</v>
+        <v>1.311199999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>10.2508</v>
+        <v>0.8932999999999995</v>
       </c>
       <c r="J7" t="n">
-        <v>13.9045</v>
+        <v>7.088799999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5483</v>
+        <v>0.7447999999999996</v>
       </c>
       <c r="L7" t="n">
-        <v>12.3557</v>
+        <v>6.343900000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-10.7703</v>
+        <v>-4.8846</v>
       </c>
       <c r="N7" t="n">
-        <v>-8.6652</v>
+        <v>0.5661999999999997</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1052</v>
+        <v>-5.4508</v>
       </c>
       <c r="P7" t="n">
-        <v>5.0027</v>
+        <v>10.8751</v>
       </c>
       <c r="Q7" t="n">
-        <v>-50.0264</v>
+        <v>-5.0025</v>
       </c>
       <c r="R7" t="n">
-        <v>55.0294</v>
+        <v>15.8776</v>
       </c>
       <c r="S7" t="n">
-        <v>49.4554</v>
+        <v>5.8167</v>
       </c>
       <c r="T7" t="n">
-        <v>36.9993</v>
+        <v>2.2413</v>
       </c>
       <c r="U7" t="n">
-        <v>12.4564</v>
+        <v>3.5756</v>
       </c>
       <c r="V7" t="n">
-        <v>-30.4858</v>
+        <v>2.1978</v>
       </c>
       <c r="W7" t="n">
-        <v>-2.1864</v>
+        <v>9.296999999999999</v>
       </c>
       <c r="X7" t="n">
-        <v>-28.2994</v>
+        <v>-7.0992</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>V. VUCETIC</t>
+          <t>X. OROZ URIA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="D8" t="n">
-        <v>23.2157</v>
+        <v>20.4226</v>
       </c>
       <c r="E8" t="n">
-        <v>16.8763</v>
+        <v>2.3437</v>
       </c>
       <c r="F8" t="n">
-        <v>6.3395</v>
+        <v>18.0792</v>
       </c>
       <c r="G8" t="n">
-        <v>2.2043</v>
+        <v>-2.003099999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>1.311199999999999</v>
+        <v>0.8683000000000005</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8932999999999995</v>
+        <v>-2.8715</v>
       </c>
       <c r="J8" t="n">
-        <v>7.088799999999999</v>
+        <v>15.643</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7447999999999996</v>
+        <v>12.5005</v>
       </c>
       <c r="L8" t="n">
-        <v>6.343900000000001</v>
+        <v>3.142000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.8846</v>
+        <v>-17.646</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5661999999999997</v>
+        <v>-11.6321</v>
       </c>
       <c r="O8" t="n">
-        <v>-5.4508</v>
+        <v>-6.013500000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>10.8751</v>
+        <v>14.3554</v>
       </c>
       <c r="Q8" t="n">
-        <v>-5.0025</v>
+        <v>-23.2728</v>
       </c>
       <c r="R8" t="n">
-        <v>15.8776</v>
+        <v>37.6284</v>
       </c>
       <c r="S8" t="n">
-        <v>7.938</v>
+        <v>10.6637</v>
       </c>
       <c r="T8" t="n">
-        <v>5.4931</v>
+        <v>4.8685</v>
       </c>
       <c r="U8" t="n">
-        <v>2.4449</v>
+        <v>5.7949</v>
       </c>
       <c r="V8" t="n">
-        <v>2.1978</v>
+        <v>-2.5928</v>
       </c>
       <c r="W8" t="n">
-        <v>9.296999999999999</v>
+        <v>5.1056</v>
       </c>
       <c r="X8" t="n">
-        <v>-7.0992</v>
+        <v>-7.6986</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X. OROZ URIA</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D9" t="n">
-        <v>18.7665</v>
+        <v>16.4899</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1295000000000002</v>
+        <v>3.629300000000002</v>
       </c>
       <c r="F9" t="n">
-        <v>18.8956</v>
+        <v>12.8609</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.003099999999999</v>
+        <v>-2.394</v>
       </c>
       <c r="H9" t="n">
-        <v>0.8683000000000005</v>
+        <v>-6.0169</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8715</v>
+        <v>3.622600000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>15.643</v>
+        <v>4.4292</v>
       </c>
       <c r="K9" t="n">
-        <v>12.5005</v>
+        <v>-1.754500000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>3.142000000000001</v>
+        <v>6.183300000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-17.646</v>
+        <v>-6.8228</v>
       </c>
       <c r="N9" t="n">
-        <v>-11.6321</v>
+        <v>-4.2622</v>
       </c>
       <c r="O9" t="n">
-        <v>-6.013500000000001</v>
+        <v>-2.560800000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>14.3554</v>
+        <v>21.0979</v>
       </c>
       <c r="Q9" t="n">
-        <v>-23.2728</v>
+        <v>-11.5278</v>
       </c>
       <c r="R9" t="n">
-        <v>37.6284</v>
+        <v>32.6258</v>
       </c>
       <c r="S9" t="n">
-        <v>9.0067</v>
+        <v>3.5362</v>
       </c>
       <c r="T9" t="n">
-        <v>2.395</v>
+        <v>0.5168</v>
       </c>
       <c r="U9" t="n">
-        <v>6.6116</v>
+        <v>3.0196</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.5928</v>
+        <v>-5.7505</v>
       </c>
       <c r="W9" t="n">
-        <v>5.1056</v>
+        <v>10.2113</v>
       </c>
       <c r="X9" t="n">
-        <v>-7.6986</v>
+        <v>-15.9616</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. UGOCHUKWU</t>
+          <t>J. GONZALEZ CALVO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D10" t="n">
-        <v>12.5923</v>
+        <v>9.027100000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>7.885699999999999</v>
+        <v>2.736199999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>4.706799999999999</v>
+        <v>6.2906</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.005000000000001</v>
+        <v>3.6262</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.0114</v>
+        <v>2.383999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>1.0062</v>
+        <v>1.2421</v>
       </c>
       <c r="J10" t="n">
-        <v>7.149100000000001</v>
+        <v>5.202</v>
       </c>
       <c r="K10" t="n">
-        <v>4.2987</v>
+        <v>3.0602</v>
       </c>
       <c r="L10" t="n">
-        <v>2.85</v>
+        <v>2.1418</v>
       </c>
       <c r="M10" t="n">
-        <v>-8.154299999999999</v>
+        <v>-1.5759</v>
       </c>
       <c r="N10" t="n">
-        <v>-6.31</v>
+        <v>-0.6763</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8441</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>4.1325</v>
+        <v>0.2175</v>
       </c>
       <c r="Q10" t="n">
-        <v>-10.2228</v>
+        <v>-6.5251</v>
       </c>
       <c r="R10" t="n">
-        <v>14.3552</v>
+        <v>6.7425</v>
       </c>
       <c r="S10" t="n">
-        <v>5.405399999999999</v>
+        <v>3.6633</v>
       </c>
       <c r="T10" t="n">
-        <v>3.9427</v>
+        <v>2.323</v>
       </c>
       <c r="U10" t="n">
-        <v>1.4623</v>
+        <v>1.3401</v>
       </c>
       <c r="V10" t="n">
-        <v>4.0596</v>
+        <v>1.5204</v>
       </c>
       <c r="W10" t="n">
-        <v>7.0165</v>
+        <v>1.7363</v>
       </c>
       <c r="X10" t="n">
-        <v>-2.9568</v>
+        <v>-0.2158999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>S. UGOCHUKWU</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>11.7825</v>
+        <v>7.628299999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6839000000000004</v>
+        <v>4.154</v>
       </c>
       <c r="F11" t="n">
-        <v>11.0987</v>
+        <v>3.4738</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.394</v>
+        <v>-1.005000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>-6.0169</v>
+        <v>-2.0114</v>
       </c>
       <c r="I11" t="n">
-        <v>3.622600000000001</v>
+        <v>1.0062</v>
       </c>
       <c r="J11" t="n">
-        <v>4.4292</v>
+        <v>7.149100000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.754500000000001</v>
+        <v>4.2987</v>
       </c>
       <c r="L11" t="n">
-        <v>6.183300000000001</v>
+        <v>2.85</v>
       </c>
       <c r="M11" t="n">
-        <v>-6.8228</v>
+        <v>-8.154299999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.2622</v>
+        <v>-6.31</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.560800000000001</v>
+        <v>-1.8441</v>
       </c>
       <c r="P11" t="n">
-        <v>21.0979</v>
+        <v>4.1325</v>
       </c>
       <c r="Q11" t="n">
-        <v>-11.5278</v>
+        <v>-10.2228</v>
       </c>
       <c r="R11" t="n">
-        <v>32.6258</v>
+        <v>14.3552</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1712</v>
+        <v>0.4409999999999998</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.4286</v>
+        <v>0.2115999999999998</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2572</v>
+        <v>0.2295</v>
       </c>
       <c r="V11" t="n">
-        <v>-5.7505</v>
+        <v>4.0596</v>
       </c>
       <c r="W11" t="n">
-        <v>10.2113</v>
+        <v>7.0165</v>
       </c>
       <c r="X11" t="n">
-        <v>-15.9616</v>
+        <v>-2.9568</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. GONZALEZ CALVO</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>10.5624</v>
+        <v>2.8355</v>
       </c>
       <c r="E12" t="n">
-        <v>4.636299999999999</v>
+        <v>0.4502000000000003</v>
       </c>
       <c r="F12" t="n">
-        <v>5.9262</v>
+        <v>2.3853</v>
       </c>
       <c r="G12" t="n">
-        <v>3.6262</v>
+        <v>17.9233</v>
       </c>
       <c r="H12" t="n">
-        <v>2.383999999999999</v>
+        <v>11.7351</v>
       </c>
       <c r="I12" t="n">
-        <v>1.2421</v>
+        <v>6.188000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>5.202</v>
+        <v>21.4376</v>
       </c>
       <c r="K12" t="n">
-        <v>3.0602</v>
+        <v>13.5582</v>
       </c>
       <c r="L12" t="n">
-        <v>2.1418</v>
+        <v>7.879200000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.5759</v>
+        <v>-3.5141</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6763</v>
+        <v>-1.8228</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8997000000000001</v>
+        <v>-1.6914</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2175</v>
+        <v>-7.1776</v>
       </c>
       <c r="Q12" t="n">
-        <v>-6.5251</v>
+        <v>-33.4961</v>
       </c>
       <c r="R12" t="n">
-        <v>6.7425</v>
+        <v>26.3182</v>
       </c>
       <c r="S12" t="n">
-        <v>5.1981</v>
+        <v>-1.2655</v>
       </c>
       <c r="T12" t="n">
-        <v>4.2229</v>
+        <v>-0.9180999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9752999999999999</v>
+        <v>-0.3476000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>1.5204</v>
+        <v>-6.6448</v>
       </c>
       <c r="W12" t="n">
-        <v>1.7363</v>
+        <v>13.4266</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2158999999999999</v>
+        <v>-20.0713</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>O. GOMEZ FERNANDEZ</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.293</v>
+        <v>-1.766000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.7906</v>
+        <v>-26.0615</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5024000000000001</v>
+        <v>24.2959</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.728</v>
+        <v>3.133900000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.1917</v>
+        <v>-7.1168</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.5363</v>
+        <v>10.2508</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.3607</v>
+        <v>13.9045</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0911</v>
+        <v>1.5483</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.452</v>
+        <v>12.3557</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3675</v>
+        <v>-10.7703</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.283</v>
+        <v>-8.6652</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.08450000000000002</v>
+        <v>-2.1052</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.4349999999999999</v>
+        <v>5.0027</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.0875</v>
+        <v>-50.0264</v>
       </c>
       <c r="R13" t="n">
-        <v>0.6525</v>
+        <v>55.0294</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0001000000000000167</v>
+        <v>20.5834</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3425</v>
+        <v>12.2468</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3424</v>
+        <v>8.3361</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.13</v>
+        <v>-30.4858</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>-2.1864</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.13</v>
+        <v>-28.2994</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>M. HERON</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.188699999999999</v>
+        <v>-2.309099999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>-3.649000000000001</v>
+        <v>-7.9218</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.539800000000001</v>
+        <v>5.6127</v>
       </c>
       <c r="G14" t="n">
-        <v>17.9233</v>
+        <v>8.372800000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>11.7351</v>
+        <v>6.381600000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>6.188000000000001</v>
+        <v>1.9914</v>
       </c>
       <c r="J14" t="n">
-        <v>21.4376</v>
+        <v>8.3804</v>
       </c>
       <c r="K14" t="n">
-        <v>13.5582</v>
+        <v>4.7137</v>
       </c>
       <c r="L14" t="n">
-        <v>7.879200000000001</v>
+        <v>3.6666</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.5141</v>
+        <v>-0.007299999999999973</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8228</v>
+        <v>1.6678</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6914</v>
+        <v>-1.6752</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.1776</v>
+        <v>-3.9152</v>
       </c>
       <c r="Q14" t="n">
-        <v>-33.4961</v>
+        <v>-18.053</v>
       </c>
       <c r="R14" t="n">
-        <v>26.3182</v>
+        <v>14.1378</v>
       </c>
       <c r="S14" t="n">
-        <v>-9.289300000000001</v>
+        <v>-0.3362000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-5.0167</v>
+        <v>-0.9408000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.2726</v>
+        <v>0.6047</v>
       </c>
       <c r="V14" t="n">
-        <v>-6.6448</v>
+        <v>-6.4308</v>
       </c>
       <c r="W14" t="n">
-        <v>13.4266</v>
+        <v>2.6918</v>
       </c>
       <c r="X14" t="n">
-        <v>-20.0713</v>
+        <v>-9.1225</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. HERON</t>
+          <t>O. GOMEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D15" t="n">
-        <v>-7.556099999999999</v>
+        <v>-3.1813</v>
       </c>
       <c r="E15" t="n">
-        <v>-10.9033</v>
+        <v>-2.6789</v>
       </c>
       <c r="F15" t="n">
-        <v>3.346900000000001</v>
+        <v>-0.5024</v>
       </c>
       <c r="G15" t="n">
-        <v>8.372800000000002</v>
+        <v>-1.728</v>
       </c>
       <c r="H15" t="n">
-        <v>6.381600000000001</v>
+        <v>-0.1917</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9914</v>
+        <v>-1.5363</v>
       </c>
       <c r="J15" t="n">
-        <v>8.3804</v>
+        <v>-1.3607</v>
       </c>
       <c r="K15" t="n">
-        <v>4.7137</v>
+        <v>0.0911</v>
       </c>
       <c r="L15" t="n">
-        <v>3.6666</v>
+        <v>-1.452</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.007299999999999973</v>
+        <v>-0.3675</v>
       </c>
       <c r="N15" t="n">
-        <v>1.6678</v>
+        <v>-0.283</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.6752</v>
+        <v>-0.08450000000000002</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.9152</v>
+        <v>-0.4349999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>-18.053</v>
+        <v>-1.0875</v>
       </c>
       <c r="R15" t="n">
-        <v>14.1378</v>
+        <v>0.6525</v>
       </c>
       <c r="S15" t="n">
-        <v>-5.5833</v>
+        <v>0.1119</v>
       </c>
       <c r="T15" t="n">
-        <v>-3.9223</v>
+        <v>-0.2307</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.6609</v>
+        <v>0.3425</v>
       </c>
       <c r="V15" t="n">
-        <v>-6.4308</v>
+        <v>-1.13</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6918</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-9.1225</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-14.7866</v>
+        <v>-11.9042</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.3184</v>
+        <v>-7.666099999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.4679</v>
+        <v>-4.2382</v>
       </c>
       <c r="G16" t="n">
         <v>-10.3747</v>
@@ -1702,13 +1702,13 @@
         <v>15.8776</v>
       </c>
       <c r="S16" t="n">
-        <v>-7.4429</v>
+        <v>-4.5608</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.9202</v>
+        <v>-3.2674</v>
       </c>
       <c r="U16" t="n">
-        <v>-3.5227</v>
+        <v>-1.2934</v>
       </c>
       <c r="V16" t="n">
         <v>-5.886299999999999</v>
@@ -1735,13 +1735,13 @@
         <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>-16.0125</v>
+        <v>-17.5789</v>
       </c>
       <c r="E17" t="n">
-        <v>-12.0582</v>
+        <v>-12.325</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.9541</v>
+        <v>-5.2538</v>
       </c>
       <c r="G17" t="n">
         <v>-0.6808000000000001</v>
@@ -1780,13 +1780,13 @@
         <v>3.6975</v>
       </c>
       <c r="S17" t="n">
-        <v>2.2056</v>
+        <v>0.6392</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4494000000000001</v>
+        <v>0.1826999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>1.756</v>
+        <v>0.4562</v>
       </c>
       <c r="V17" t="n">
         <v>-5.7918</v>
@@ -1813,13 +1813,13 @@
         <v>32</v>
       </c>
       <c r="D18" t="n">
-        <v>340.3156</v>
+        <v>362.4683000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>158.677</v>
+        <v>165.1841</v>
       </c>
       <c r="F18" t="n">
-        <v>181.6381</v>
+        <v>197.2837</v>
       </c>
       <c r="G18" t="n">
         <v>195.4052</v>
@@ -1843,10 +1843,10 @@
         <v>-152.3625</v>
       </c>
       <c r="N18" t="n">
-        <v>-90.42789999999999</v>
+        <v>-90.42790000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-61.93410000000001</v>
+        <v>-61.9341</v>
       </c>
       <c r="P18" t="n">
         <v>104.4019</v>
@@ -1858,16 +1858,16 @@
         <v>491.5636</v>
       </c>
       <c r="S18" t="n">
-        <v>46.50529999999999</v>
+        <v>68.6598</v>
       </c>
       <c r="T18" t="n">
-        <v>18.4068</v>
+        <v>24.9141</v>
       </c>
       <c r="U18" t="n">
-        <v>28.0989</v>
+        <v>43.7442</v>
       </c>
       <c r="V18" t="n">
-        <v>-5.998700000000007</v>
+        <v>-5.998699999999999</v>
       </c>
       <c r="W18" t="n">
         <v>179.6646</v>
